--- a/artfynd/A 21253-2024 artfynd.xlsx
+++ b/artfynd/A 21253-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126430405</v>
       </c>
       <c r="B2" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
